--- a/publish/Radhika_Nepali/questions.xlsx
+++ b/publish/Radhika_Nepali/questions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anuj\opnsrc_try\ai\QuizWeb_Manual\publish\Radhika_Nepali\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anuj\opnsrc_try\ai\QuizWeb_Manual\publish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BD702A-1E84-466B-87C3-8EAE2C53C6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F988492E-D102-419F-98D8-43D4626BD81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="679">
   <si>
     <t>Class: 9</t>
   </si>
@@ -73,6 +73,9 @@
     <t>1</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>What does HTML stand for?</t>
   </si>
   <si>
@@ -164,6 +167,1896 @@
   </si>
   <si>
     <t>hl</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create a paragraph?</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>&lt;para&gt;</t>
+  </si>
+  <si>
+    <t>&lt;pt&gt;</t>
+  </si>
+  <si>
+    <t>&lt;text&gt;</t>
+  </si>
+  <si>
+    <t>&lt;pg&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Which tag is used for the largest heading in HTML?</t>
+  </si>
+  <si>
+    <t>&lt;h1&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h6&gt;</t>
+  </si>
+  <si>
+    <t>&lt;hd&gt;</t>
+  </si>
+  <si>
+    <t>&lt;heading&gt;</t>
+  </si>
+  <si>
+    <t>&lt;hbig&gt;</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create an unordered list?</t>
+  </si>
+  <si>
+    <t>&lt;ol&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ul&gt;</t>
+  </si>
+  <si>
+    <t>&lt;li&gt;</t>
+  </si>
+  <si>
+    <t>&lt;list&gt;</t>
+  </si>
+  <si>
+    <t>&lt;unlist&gt;</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create an ordered list?</t>
+  </si>
+  <si>
+    <t>&lt;ord&gt;</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create a list item?</t>
+  </si>
+  <si>
+    <t>&lt;item&gt;</t>
+  </si>
+  <si>
+    <t>&lt;line&gt;</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create a table?</t>
+  </si>
+  <si>
+    <t>&lt;td&gt;</t>
+  </si>
+  <si>
+    <t>&lt;tr&gt;</t>
+  </si>
+  <si>
+    <t>&lt;th&gt;</t>
+  </si>
+  <si>
+    <t>&lt;tab&gt;</t>
+  </si>
+  <si>
+    <t>&lt;table&gt;</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Which HTML tag creates a row in a table?</t>
+  </si>
+  <si>
+    <t>&lt;row&gt;</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Which HTML tag creates a header cell in a table?</t>
+  </si>
+  <si>
+    <t>&lt;header&gt;</t>
+  </si>
+  <si>
+    <t>&lt;table-head&gt;</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Which HTML tag creates a data cell in a table?</t>
+  </si>
+  <si>
+    <t>&lt;data&gt;</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to insert an image into a web page?</t>
+  </si>
+  <si>
+    <t>&lt;pic&gt;</t>
+  </si>
+  <si>
+    <t>&lt;picture&gt;</t>
+  </si>
+  <si>
+    <t>&lt;image&gt;</t>
+  </si>
+  <si>
+    <t>&lt;img&gt;</t>
+  </si>
+  <si>
+    <t>&lt;photo&gt;</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Which attribute specifies the file name of an image in the &lt;img&gt; tag?</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Which attribute provides alternative text for an image if it fails to load?</t>
+  </si>
+  <si>
+    <t>srcset</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create a form for collecting user input?</t>
+  </si>
+  <si>
+    <t>&lt;input&gt;</t>
+  </si>
+  <si>
+    <t>&lt;form&gt;</t>
+  </si>
+  <si>
+    <t>&lt;field&gt;</t>
+  </si>
+  <si>
+    <t>&lt;area&gt;</t>
+  </si>
+  <si>
+    <t>&lt;label&gt;</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create a text input field?</t>
+  </si>
+  <si>
+    <t>&lt;write&gt;</t>
+  </si>
+  <si>
+    <t>&lt;box&gt;</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create a drop-down list?</t>
+  </si>
+  <si>
+    <t>&lt;dropdown&gt;</t>
+  </si>
+  <si>
+    <t>&lt;option&gt;</t>
+  </si>
+  <si>
+    <t>&lt;select&gt;</t>
+  </si>
+  <si>
+    <t>&lt;menu&gt;</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create a division or container in a document?</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;container&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div&gt;</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Which tag is used to create a line break in HTML?</t>
+  </si>
+  <si>
+    <t>&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>&lt;lb&gt;</t>
+  </si>
+  <si>
+    <t>&lt;break&gt;</t>
+  </si>
+  <si>
+    <t>&lt;hr&gt;</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Which tag is used to draw a horizontal line in HTML?</t>
+  </si>
+  <si>
+    <t>&lt;hline&gt;</t>
+  </si>
+  <si>
+    <t>&lt;separator&gt;</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Which tag makes text bold in HTML?</t>
+  </si>
+  <si>
+    <t>&lt;strongly&gt;</t>
+  </si>
+  <si>
+    <t>&lt;bold&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;dark&gt;</t>
+  </si>
+  <si>
+    <t>&lt;fat&gt;</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Which tag makes text italic in HTML?</t>
+  </si>
+  <si>
+    <t>&lt;it&gt;</t>
+  </si>
+  <si>
+    <t>&lt;slanted&gt;</t>
+  </si>
+  <si>
+    <t>&lt;emph&gt;</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;</t>
+  </si>
+  <si>
+    <t>&lt;italics&gt;</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to write subscript text?</t>
+  </si>
+  <si>
+    <t>&lt;sup&gt;</t>
+  </si>
+  <si>
+    <t>&lt;down&gt;</t>
+  </si>
+  <si>
+    <t>&lt;below&gt;</t>
+  </si>
+  <si>
+    <t>&lt;small&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to write superscript text?</t>
+  </si>
+  <si>
+    <t>&lt;up&gt;</t>
+  </si>
+  <si>
+    <t>&lt;above&gt;</t>
+  </si>
+  <si>
+    <t>&lt;high&gt;</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Which tag contains the main visible content of a webpage?</t>
+  </si>
+  <si>
+    <t>&lt;head&gt;</t>
+  </si>
+  <si>
+    <t>&lt;body&gt;</t>
+  </si>
+  <si>
+    <t>&lt;title&gt;</t>
+  </si>
+  <si>
+    <t>&lt;main&gt;</t>
+  </si>
+  <si>
+    <t>&lt;html&gt;</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Which tag contains the title and metadata of an HTML document?</t>
+  </si>
+  <si>
+    <t>&lt;meta&gt;</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to link an external stylesheet?</t>
+  </si>
+  <si>
+    <t>&lt;style&gt;</t>
+  </si>
+  <si>
+    <t>&lt;link rel&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sheet&gt;</t>
+  </si>
+  <si>
+    <t>&lt;css]</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Which attribute opens a hyperlink in a new browser tab?</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>What does CSS stand for?</t>
+  </si>
+  <si>
+    <t>Cascading Style Sheets</t>
+  </si>
+  <si>
+    <t>Computer Style System</t>
+  </si>
+  <si>
+    <t>Creative Style Sheets</t>
+  </si>
+  <si>
+    <t>Color and Style System</t>
+  </si>
+  <si>
+    <t>Cascading Size Sheets</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>What is CSS mainly used for?</t>
+  </si>
+  <si>
+    <t>Writing web page content</t>
+  </si>
+  <si>
+    <t>Styling the appearance of web pages</t>
+  </si>
+  <si>
+    <t>Creating computer programs</t>
+  </si>
+  <si>
+    <t>Storing data in databases</t>
+  </si>
+  <si>
+    <t>Sending emails</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Which type of CSS is written directly inside an HTML element?</t>
+  </si>
+  <si>
+    <t>External CSS</t>
+  </si>
+  <si>
+    <t>Internal CSS</t>
+  </si>
+  <si>
+    <t>Inline CSS</t>
+  </si>
+  <si>
+    <t>Embedded HTML</t>
+  </si>
+  <si>
+    <t>Global CSS</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Which type of CSS is written inside the &lt;style&gt; tag in the head section?</t>
+  </si>
+  <si>
+    <t>Local CSS</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Which type of CSS is written in a separate .css file?</t>
+  </si>
+  <si>
+    <t>Embedded CSS</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Which attribute is used to apply inline CSS to an element?</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>css</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Which CSS property is used to change the text colour?</t>
+  </si>
+  <si>
+    <t>text-color</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>font-color</t>
+  </si>
+  <si>
+    <t>background-color</t>
+  </si>
+  <si>
+    <t>text-style</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Which CSS property is used to set the background colour of an element?</t>
+  </si>
+  <si>
+    <t>bgcolor</t>
+  </si>
+  <si>
+    <t>fill</t>
+  </si>
+  <si>
+    <t>shade</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Which CSS property is used to change the size of text?</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>text-size</t>
+  </si>
+  <si>
+    <t>font-height</t>
+  </si>
+  <si>
+    <t>font-size</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Which CSS property is used to change the font typeface of text?</t>
+  </si>
+  <si>
+    <t>font-type</t>
+  </si>
+  <si>
+    <t>text-font</t>
+  </si>
+  <si>
+    <t>typeface</t>
+  </si>
+  <si>
+    <t>font</t>
+  </si>
+  <si>
+    <t>font-family</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Which CSS property is used to make text bold?</t>
+  </si>
+  <si>
+    <t>font-weight</t>
+  </si>
+  <si>
+    <t>font-bold</t>
+  </si>
+  <si>
+    <t>text-weight</t>
+  </si>
+  <si>
+    <t>bold</t>
+  </si>
+  <si>
+    <t>font-style</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Which CSS property creates rounded corners on an element?</t>
+  </si>
+  <si>
+    <t>corner-round</t>
+  </si>
+  <si>
+    <t>border-radius</t>
+  </si>
+  <si>
+    <t>round-border</t>
+  </si>
+  <si>
+    <t>radius</t>
+  </si>
+  <si>
+    <t>curve</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Which CSS property sets the space between the content and the border of an element?</t>
+  </si>
+  <si>
+    <t>margin</t>
+  </si>
+  <si>
+    <t>spacing</t>
+  </si>
+  <si>
+    <t>padding</t>
+  </si>
+  <si>
+    <t>gap</t>
+  </si>
+  <si>
+    <t>space</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Which CSS property sets the space outside the border of an element?</t>
+  </si>
+  <si>
+    <t>outside</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Which selector is used to target an element by its id in CSS?</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(empty)</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>:</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>What is the Internet?</t>
+  </si>
+  <si>
+    <t>A global network of interconnected computers</t>
+  </si>
+  <si>
+    <t>A single computer in a school</t>
+  </si>
+  <si>
+    <t>A type of web browser</t>
+  </si>
+  <si>
+    <t>A computer program</t>
+  </si>
+  <si>
+    <t>A mobile phone network</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>What does WWW stand for?</t>
+  </si>
+  <si>
+    <t>World Web Wide</t>
+  </si>
+  <si>
+    <t>World Wide Web</t>
+  </si>
+  <si>
+    <t>Web World Wide</t>
+  </si>
+  <si>
+    <t>World Wide Website</t>
+  </si>
+  <si>
+    <t>Wide Web World</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>A software program used to access and view websites is called a:</t>
+  </si>
+  <si>
+    <t>Search engine</t>
+  </si>
+  <si>
+    <t>Operating system</t>
+  </si>
+  <si>
+    <t>Web browser</t>
+  </si>
+  <si>
+    <t>Compiler</t>
+  </si>
+  <si>
+    <t>Modem</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Which of the following is a web browser?</t>
+  </si>
+  <si>
+    <t>Google Search</t>
+  </si>
+  <si>
+    <t>Google Drive</t>
+  </si>
+  <si>
+    <t>Google Docs</t>
+  </si>
+  <si>
+    <t>Google Chrome</t>
+  </si>
+  <si>
+    <t>Google Maps</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>A program or service used to find information on the Internet is called a:</t>
+  </si>
+  <si>
+    <t>Website</t>
+  </si>
+  <si>
+    <t>Protocol</t>
+  </si>
+  <si>
+    <t>Server</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Which of the following is a search engine?</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>Chrome</t>
+  </si>
+  <si>
+    <t>Notepad</t>
+  </si>
+  <si>
+    <t>Windows</t>
+  </si>
+  <si>
+    <t>VLC</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>What does URL stand for?</t>
+  </si>
+  <si>
+    <t>Universal Resource Link</t>
+  </si>
+  <si>
+    <t>Uniform Resource Locator</t>
+  </si>
+  <si>
+    <t>Uniform Resource Link</t>
+  </si>
+  <si>
+    <t>Universal Reference Locator</t>
+  </si>
+  <si>
+    <t>Unique Resource Location</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>A URL is the ______ of a resource available on the Internet.</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Colour</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Which protocol is more secure for accessing websites?</t>
+  </si>
+  <si>
+    <t>HTTP</t>
+  </si>
+  <si>
+    <t>FTP</t>
+  </si>
+  <si>
+    <t>SMTP</t>
+  </si>
+  <si>
+    <t>HTTPS</t>
+  </si>
+  <si>
+    <t>Telnet</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>What does HTTP stand for?</t>
+  </si>
+  <si>
+    <t>HyperText Transport Program</t>
+  </si>
+  <si>
+    <t>High Text Transfer Protocol</t>
+  </si>
+  <si>
+    <t>Home Text Transfer Protocol</t>
+  </si>
+  <si>
+    <t>Hyperlink Transfer Protocol</t>
+  </si>
+  <si>
+    <t>HyperText Transfer Protocol</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>What does HTTPS stand for?</t>
+  </si>
+  <si>
+    <t>HyperText Transfer Protocol Secure</t>
+  </si>
+  <si>
+    <t>HyperText Transfer Protocol Server</t>
+  </si>
+  <si>
+    <t>High Transfer Protocol Secure</t>
+  </si>
+  <si>
+    <t>Hyperlink Transfer Protocol System</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>HTTPS keeps communication secure by encrypting data using:</t>
+  </si>
+  <si>
+    <t>SSL/TLS</t>
+  </si>
+  <si>
+    <t>HTML</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>Which protocol is commonly used to transfer files between computers on a network?</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>Which protocol is used to send email from a client to a mail server?</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>A collection of related web pages under one name is called a:</t>
+  </si>
+  <si>
+    <t>Web server</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>The first page that opens when you visit a website is called the:</t>
+  </si>
+  <si>
+    <t>Home page</t>
+  </si>
+  <si>
+    <t>Index page</t>
+  </si>
+  <si>
+    <t>Start page</t>
+  </si>
+  <si>
+    <t>Front page</t>
+  </si>
+  <si>
+    <t>Main page</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>The World Wide Web (WWW) was invented by:</t>
+  </si>
+  <si>
+    <t>Bill Gates</t>
+  </si>
+  <si>
+    <t>Tim Berners-Lee</t>
+  </si>
+  <si>
+    <t>Steve Jobs</t>
+  </si>
+  <si>
+    <t>Charles Babbage</t>
+  </si>
+  <si>
+    <t>Alan Turing</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>A word or phrase or image that you click to jump to another page is called a:</t>
+  </si>
+  <si>
+    <t>Web page</t>
+  </si>
+  <si>
+    <t>Browser</t>
+  </si>
+  <si>
+    <t>Hyperlink</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>The address of a website typed in the browser's address bar is its:</t>
+  </si>
+  <si>
+    <t>WWW</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>In the URL https://www.google.com, the domain name is:</t>
+  </si>
+  <si>
+    <t>https</t>
+  </si>
+  <si>
+    <t>www</t>
+  </si>
+  <si>
+    <t>com</t>
+  </si>
+  <si>
+    <t>google</t>
+  </si>
+  <si>
+    <t>google.com</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>In a web address, "https" means the connection is:</t>
+  </si>
+  <si>
+    <t>Secure and encrypted</t>
+  </si>
+  <si>
+    <t>Unsafe</t>
+  </si>
+  <si>
+    <t>Slow</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>Which of the following is a valid web address (URL) format?</t>
+  </si>
+  <si>
+    <t>www.example</t>
+  </si>
+  <si>
+    <t>https://www.example.com</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>com.example</t>
+  </si>
+  <si>
+    <t>//example</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>Which device is commonly used to connect a computer to the Internet at home?</t>
+  </si>
+  <si>
+    <t>Printer</t>
+  </si>
+  <si>
+    <t>Scanner</t>
+  </si>
+  <si>
+    <t>Modem or router</t>
+  </si>
+  <si>
+    <t>Projector</t>
+  </si>
+  <si>
+    <t>Speaker</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>Web pages on the Internet are written mainly in:</t>
+  </si>
+  <si>
+    <t>C++</t>
+  </si>
+  <si>
+    <t>Java</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Pascal</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>A search engine finds web pages by:</t>
+  </si>
+  <si>
+    <t>Storing them on a CD</t>
+  </si>
+  <si>
+    <t>Asking users to type URLs</t>
+  </si>
+  <si>
+    <t>Using satellite signals</t>
+  </si>
+  <si>
+    <t>Browsing email</t>
+  </si>
+  <si>
+    <t>Searching and indexing the web using keywords</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>Which software is commonly used for remote login and remote computer access?</t>
+  </si>
+  <si>
+    <t>AnyDesk</t>
+  </si>
+  <si>
+    <t>Calculator</t>
+  </si>
+  <si>
+    <t>Paint</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>AnyDesk is mainly used to:</t>
+  </si>
+  <si>
+    <t>Edit photos</t>
+  </si>
+  <si>
+    <t>Control a computer from a remote location</t>
+  </si>
+  <si>
+    <t>Play games</t>
+  </si>
+  <si>
+    <t>Record audio</t>
+  </si>
+  <si>
+    <t>Write documents</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>Which of the following is a video conferencing tool?</t>
+  </si>
+  <si>
+    <t>Google Meet</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>Zoom and Microsoft Teams are commonly used for:</t>
+  </si>
+  <si>
+    <t>Designing graphics</t>
+  </si>
+  <si>
+    <t>Compiling programs</t>
+  </si>
+  <si>
+    <t>Storing files</t>
+  </si>
+  <si>
+    <t>Video conferencing and online meetings</t>
+  </si>
+  <si>
+    <t>Browsing the web</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>In an online meeting, the "Mute" button is used to:</t>
+  </si>
+  <si>
+    <t>Turn off your camera</t>
+  </si>
+  <si>
+    <t>End the meeting</t>
+  </si>
+  <si>
+    <t>Share the screen</t>
+  </si>
+  <si>
+    <t>Record the meeting</t>
+  </si>
+  <si>
+    <t>Turn off your microphone</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>Remote desktop software allows a person to:</t>
+  </si>
+  <si>
+    <t>Access and control another computer over the Internet</t>
+  </si>
+  <si>
+    <t>Print documents on a network</t>
+  </si>
+  <si>
+    <t>Play CD-ROMs</t>
+  </si>
+  <si>
+    <t>Defragment the hard disk</t>
+  </si>
+  <si>
+    <t>Install drivers</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>Which of the following is NOT a remote access tool?</t>
+  </si>
+  <si>
+    <t>TeamViewer</t>
+  </si>
+  <si>
+    <t>Chrome Remote Desktop</t>
+  </si>
+  <si>
+    <t>AnyDesk Remote</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>Which tool is often used for screen sharing during an online class?</t>
+  </si>
+  <si>
+    <t>Zoom</t>
+  </si>
+  <si>
+    <t>Word Processor</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>Remote access between two computers generally requires:</t>
+  </si>
+  <si>
+    <t>A printer</t>
+  </si>
+  <si>
+    <t>A scanner</t>
+  </si>
+  <si>
+    <t>A projector</t>
+  </si>
+  <si>
+    <t>An Internet connection between both computers</t>
+  </si>
+  <si>
+    <t>A television</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Which of the following is NOT a video conferencing application?</t>
+  </si>
+  <si>
+    <t>Microsoft Teams</t>
+  </si>
+  <si>
+    <t>Skype</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>UI stands for:</t>
+  </si>
+  <si>
+    <t>User Interface</t>
+  </si>
+  <si>
+    <t>User Internet</t>
+  </si>
+  <si>
+    <t>Universal Interface</t>
+  </si>
+  <si>
+    <t>User Input</t>
+  </si>
+  <si>
+    <t>Under Interface</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>UX stands for:</t>
+  </si>
+  <si>
+    <t>User External</t>
+  </si>
+  <si>
+    <t>User Experience</t>
+  </si>
+  <si>
+    <t>Universal Experience</t>
+  </si>
+  <si>
+    <t>User Expression</t>
+  </si>
+  <si>
+    <t>Unified Extension</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>The main purpose of UX design is to:</t>
+  </si>
+  <si>
+    <t>Write computer programs</t>
+  </si>
+  <si>
+    <t>Increase Internet speed</t>
+  </si>
+  <si>
+    <t>Improve the user's overall experience</t>
+  </si>
+  <si>
+    <t>Create databases</t>
+  </si>
+  <si>
+    <t>Design microchips</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>The main purpose of UI design is to:</t>
+  </si>
+  <si>
+    <t>Manage network cables</t>
+  </si>
+  <si>
+    <t>Write HTML documents</t>
+  </si>
+  <si>
+    <t>Compile code</t>
+  </si>
+  <si>
+    <t>Design the visual layout the user interacts with</t>
+  </si>
+  <si>
+    <t>Test hardware</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>A wireframe is best described as:</t>
+  </si>
+  <si>
+    <t>A finished, fully coded website</t>
+  </si>
+  <si>
+    <t>A type of web server</t>
+  </si>
+  <si>
+    <t>A programming language</t>
+  </si>
+  <si>
+    <t>A search engine</t>
+  </si>
+  <si>
+    <t>A basic visual layout or skeleton of a webpage or app</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>Social media is best described as a platform for:</t>
+  </si>
+  <si>
+    <t>Sharing content and interacting with others online</t>
+  </si>
+  <si>
+    <t>Storing hardware components</t>
+  </si>
+  <si>
+    <t>Installing software</t>
+  </si>
+  <si>
+    <t>Sending physical mail</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>Sharing your password publicly on social media is:</t>
+  </si>
+  <si>
+    <t>A safe practice</t>
+  </si>
+  <si>
+    <t>An unsafe practice</t>
+  </si>
+  <si>
+    <t>Required by law</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Recommended by teachers</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>Which of the following is a social media platform?</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>PowerPoint</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>A blog is best described as:</t>
+  </si>
+  <si>
+    <t>A type of hardware</t>
+  </si>
+  <si>
+    <t>An email address</t>
+  </si>
+  <si>
+    <t>A website with regularly updated articles or posts</t>
+  </si>
+  <si>
+    <t>A computer virus</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>Using the Internet to harass or threaten someone is called:</t>
+  </si>
+  <si>
+    <t>Browsing</t>
+  </si>
+  <si>
+    <t>Downloading</t>
+  </si>
+  <si>
+    <t>Uploading</t>
+  </si>
+  <si>
+    <t>Cyberbullying</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>Which of the following is a good password practice?</t>
+  </si>
+  <si>
+    <t>Using a strong, unique password</t>
+  </si>
+  <si>
+    <t>Using your date of birth</t>
+  </si>
+  <si>
+    <t>Sharing it with friends</t>
+  </si>
+  <si>
+    <t>Using 'password' as your password</t>
+  </si>
+  <si>
+    <t>Keeping the same password for every account</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>Clicking unknown links from suspicious websites is:</t>
+  </si>
+  <si>
+    <t>Usually safe</t>
+  </si>
+  <si>
+    <t>Unsafe and should be avoided</t>
+  </si>
+  <si>
+    <t>Required for studying</t>
+  </si>
+  <si>
+    <t>A good way to earn money</t>
+  </si>
+  <si>
+    <t>Recommended by experts</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>Which action helps protect your privacy online?</t>
+  </si>
+  <si>
+    <t>Posting your address online</t>
+  </si>
+  <si>
+    <t>Sending passwords to friends</t>
+  </si>
+  <si>
+    <t>Not sharing personal details publicly</t>
+  </si>
+  <si>
+    <t>Accepting every friend request</t>
+  </si>
+  <si>
+    <t>Sharing your phone number</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>A "digital footprint" is best described as:</t>
+  </si>
+  <si>
+    <t>A type of computer virus</t>
+  </si>
+  <si>
+    <t>A software update</t>
+  </si>
+  <si>
+    <t>A storage device</t>
+  </si>
+  <si>
+    <t>The trail of data you leave behind online</t>
+  </si>
+  <si>
+    <t>A web browser</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>Which is a benefit of the Internet for students?</t>
+  </si>
+  <si>
+    <t>Wasting time on games only</t>
+  </si>
+  <si>
+    <t>Sending physical letters</t>
+  </si>
+  <si>
+    <t>Increasing pollution</t>
+  </si>
+  <si>
+    <t>Slowing down computers</t>
+  </si>
+  <si>
+    <t>Access to information and educational resources</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>WDLC stands for:</t>
+  </si>
+  <si>
+    <t>Web Development Life Cycle</t>
+  </si>
+  <si>
+    <t>Web Design and Layout Concept</t>
+  </si>
+  <si>
+    <t>Web Data Link Control</t>
+  </si>
+  <si>
+    <t>Web Document Language Code</t>
+  </si>
+  <si>
+    <t>Web Development Language Cycle</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>The first step in the WDLC is usually:</t>
+  </si>
+  <si>
+    <t>Debugging</t>
+  </si>
+  <si>
+    <t>Planning and analysis</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>Publishing</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>In WDLC, the designing step mainly involves:</t>
+  </si>
+  <si>
+    <t>Writing the final code</t>
+  </si>
+  <si>
+    <t>Fixing bugs</t>
+  </si>
+  <si>
+    <t>Creating the layout, wireframe or prototype</t>
+  </si>
+  <si>
+    <t>Promoting the site</t>
+  </si>
+  <si>
+    <t>Buying hardware</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>In WDLC, the step where the website is actually coded is called:</t>
+  </si>
+  <si>
+    <t>Planning</t>
+  </si>
+  <si>
+    <t>Implementation or development</t>
+  </si>
+  <si>
+    <t>Analysis</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Testing a website is done to:</t>
+  </si>
+  <si>
+    <t>Delete the old website</t>
+  </si>
+  <si>
+    <t>Sell the website</t>
+  </si>
+  <si>
+    <t>Design the layout</t>
+  </si>
+  <si>
+    <t>Choose colours</t>
+  </si>
+  <si>
+    <t>Check that it works correctly without errors</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Publishing or deployment of a website means:</t>
+  </si>
+  <si>
+    <t>Making the website available on the Internet</t>
+  </si>
+  <si>
+    <t>Writing the HTML code</t>
+  </si>
+  <si>
+    <t>Designing wireframes</t>
+  </si>
+  <si>
+    <t>Testing the code</t>
+  </si>
+  <si>
+    <t>Collecting requirements</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>Which of the following is a step in the WDLC?</t>
+  </si>
+  <si>
+    <t>Printing</t>
+  </si>
+  <si>
+    <t>Drawing</t>
+  </si>
+  <si>
+    <t>Singing</t>
+  </si>
+  <si>
+    <t>Saving money</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>A web developer mainly uses which languages to build a basic website?</t>
+  </si>
+  <si>
+    <t>Python and C++</t>
+  </si>
+  <si>
+    <t>C++ and Pascal</t>
+  </si>
+  <si>
+    <t>HTML, CSS and JavaScript</t>
+  </si>
+  <si>
+    <t>SQL and Excel</t>
+  </si>
+  <si>
+    <t>Photoshop and Paint</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>Updating a website regularly to keep it working is part of:</t>
+  </si>
+  <si>
+    <t>Designing</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>A good website should be:</t>
+  </si>
+  <si>
+    <t>Very slow and confusing</t>
+  </si>
+  <si>
+    <t>Full of pop-up ads</t>
+  </si>
+  <si>
+    <t>With no text</t>
+  </si>
+  <si>
+    <t>Impossible to open</t>
+  </si>
+  <si>
+    <t>Easy to navigate and fast to load</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to write JavaScript inside a web page?</t>
+  </si>
+  <si>
+    <t>&lt;script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;javascript&gt;</t>
+  </si>
+  <si>
+    <t>&lt;code&gt;</t>
+  </si>
+  <si>
+    <t>&lt;run&gt;</t>
+  </si>
+  <si>
+    <t>&lt;js&gt;</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>Which keyboard key refreshes or reloads a web page?</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>F5</t>
+  </si>
+  <si>
+    <t>F12</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>Esc</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>HTML files are usually saved with the file extension:</t>
+  </si>
+  <si>
+    <t>.pdf</t>
+  </si>
+  <si>
+    <t>.jpg</t>
+  </si>
+  <si>
+    <t>.html</t>
+  </si>
+  <si>
+    <t>.docx</t>
+  </si>
+  <si>
+    <t>.exe</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Which of the following is a top-level domain?</t>
+  </si>
+  <si>
+    <t>http</t>
+  </si>
+  <si>
+    <t>html</t>
+  </si>
+  <si>
+    <t>.com</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>An ordered list in HTML displays items with:</t>
+  </si>
+  <si>
+    <t>Circles</t>
+  </si>
+  <si>
+    <t>Squares</t>
+  </si>
+  <si>
+    <t>Dashes</t>
+  </si>
+  <si>
+    <t>Check marks</t>
+  </si>
+  <si>
+    <t>Numbers</t>
   </si>
 </sst>
 </file>
@@ -1004,7 +2897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
@@ -1068,103 +2961,3060 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" t="s">
+        <v>69</v>
+      </c>
+      <c r="J12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" t="s">
         <v>43</v>
       </c>
-      <c r="G8" t="s">
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" t="s">
+        <v>68</v>
+      </c>
+      <c r="J13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" t="s">
+        <v>82</v>
+      </c>
+      <c r="I14" t="s">
+        <v>83</v>
+      </c>
+      <c r="J14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" t="s">
+        <v>81</v>
+      </c>
+      <c r="I16" t="s">
+        <v>90</v>
+      </c>
+      <c r="J16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" t="s">
+        <v>98</v>
+      </c>
+      <c r="H18" t="s">
+        <v>99</v>
+      </c>
+      <c r="I18" t="s">
+        <v>100</v>
+      </c>
+      <c r="J18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J19" t="s">
         <v>44</v>
       </c>
-      <c r="H8" t="s">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" t="s">
         <v>45</v>
       </c>
-      <c r="I8" t="s">
+      <c r="G20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" t="s">
+        <v>109</v>
+      </c>
+      <c r="J20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" t="s">
+        <v>113</v>
+      </c>
+      <c r="G21" t="s">
+        <v>114</v>
+      </c>
+      <c r="H21" t="s">
+        <v>115</v>
+      </c>
+      <c r="I21" t="s">
+        <v>116</v>
+      </c>
+      <c r="J21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" t="s">
+        <v>113</v>
+      </c>
+      <c r="I22" t="s">
+        <v>115</v>
+      </c>
+      <c r="J22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" t="s">
+        <v>125</v>
+      </c>
+      <c r="I23" t="s">
+        <v>126</v>
+      </c>
+      <c r="J23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" t="s">
+        <v>130</v>
+      </c>
+      <c r="G24" t="s">
+        <v>131</v>
+      </c>
+      <c r="H24" t="s">
+        <v>121</v>
+      </c>
+      <c r="I24" t="s">
+        <v>132</v>
+      </c>
+      <c r="J24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25" t="s">
+        <v>137</v>
+      </c>
+      <c r="H25" t="s">
+        <v>138</v>
+      </c>
+      <c r="I25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J25" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C26" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" t="s">
+        <v>136</v>
+      </c>
+      <c r="G26" t="s">
+        <v>139</v>
+      </c>
+      <c r="H26" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" t="s">
+        <v>142</v>
+      </c>
+      <c r="J26" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" t="s">
+        <v>145</v>
+      </c>
+      <c r="E27" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" t="s">
+        <v>146</v>
+      </c>
+      <c r="G27" t="s">
+        <v>147</v>
+      </c>
+      <c r="H27" t="s">
+        <v>148</v>
+      </c>
+      <c r="I27" t="s">
+        <v>149</v>
+      </c>
+      <c r="J27" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C28" t="s">
+        <v>152</v>
+      </c>
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" t="s">
+        <v>153</v>
+      </c>
+      <c r="G28" t="s">
+        <v>154</v>
+      </c>
+      <c r="H28" t="s">
+        <v>155</v>
+      </c>
+      <c r="I28" t="s">
+        <v>156</v>
+      </c>
+      <c r="J28" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>158</v>
+      </c>
+      <c r="C29" t="s">
+        <v>159</v>
+      </c>
+      <c r="D29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" t="s">
+        <v>160</v>
+      </c>
+      <c r="G29" t="s">
+        <v>161</v>
+      </c>
+      <c r="H29" t="s">
+        <v>162</v>
+      </c>
+      <c r="I29" t="s">
+        <v>163</v>
+      </c>
+      <c r="J29" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>165</v>
+      </c>
+      <c r="C30" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
+        <v>160</v>
+      </c>
+      <c r="G30" t="s">
+        <v>164</v>
+      </c>
+      <c r="H30" t="s">
+        <v>167</v>
+      </c>
+      <c r="I30" t="s">
+        <v>168</v>
+      </c>
+      <c r="J30" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>170</v>
+      </c>
+      <c r="C31" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" t="s">
+        <v>172</v>
+      </c>
+      <c r="G31" t="s">
+        <v>173</v>
+      </c>
+      <c r="H31" t="s">
+        <v>174</v>
+      </c>
+      <c r="I31" t="s">
+        <v>175</v>
+      </c>
+      <c r="J31" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" t="s">
+        <v>178</v>
+      </c>
+      <c r="D32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s">
+        <v>35</v>
+      </c>
+      <c r="F32" t="s">
+        <v>173</v>
+      </c>
+      <c r="G32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" t="s">
+        <v>172</v>
+      </c>
+      <c r="I32" t="s">
+        <v>90</v>
+      </c>
+      <c r="J32" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>180</v>
+      </c>
+      <c r="C33" t="s">
+        <v>181</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
+        <v>43</v>
+      </c>
+      <c r="F33" t="s">
+        <v>182</v>
+      </c>
+      <c r="G33" t="s">
+        <v>183</v>
+      </c>
+      <c r="H33" t="s">
+        <v>184</v>
+      </c>
+      <c r="I33" t="s">
+        <v>36</v>
+      </c>
+      <c r="J33" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s">
+        <v>51</v>
+      </c>
+      <c r="F34" t="s">
+        <v>188</v>
+      </c>
+      <c r="G34" t="s">
+        <v>189</v>
+      </c>
+      <c r="H34" t="s">
+        <v>190</v>
+      </c>
+      <c r="I34" t="s">
+        <v>44</v>
+      </c>
+      <c r="J34" t="s">
         <v>46</v>
       </c>
-      <c r="J8" t="s">
-        <v>47</v>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>191</v>
+      </c>
+      <c r="C35" t="s">
+        <v>192</v>
+      </c>
+      <c r="D35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" t="s">
+        <v>193</v>
+      </c>
+      <c r="G35" t="s">
+        <v>194</v>
+      </c>
+      <c r="H35" t="s">
+        <v>195</v>
+      </c>
+      <c r="I35" t="s">
+        <v>196</v>
+      </c>
+      <c r="J35" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>198</v>
+      </c>
+      <c r="C36" t="s">
+        <v>199</v>
+      </c>
+      <c r="D36" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" t="s">
+        <v>200</v>
+      </c>
+      <c r="G36" t="s">
+        <v>201</v>
+      </c>
+      <c r="H36" t="s">
+        <v>202</v>
+      </c>
+      <c r="I36" t="s">
+        <v>203</v>
+      </c>
+      <c r="J36" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>205</v>
+      </c>
+      <c r="C37" t="s">
+        <v>206</v>
+      </c>
+      <c r="D37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" t="s">
+        <v>207</v>
+      </c>
+      <c r="G37" t="s">
+        <v>208</v>
+      </c>
+      <c r="H37" t="s">
+        <v>209</v>
+      </c>
+      <c r="I37" t="s">
+        <v>210</v>
+      </c>
+      <c r="J37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>212</v>
+      </c>
+      <c r="C38" t="s">
+        <v>213</v>
+      </c>
+      <c r="E38" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" t="s">
+        <v>209</v>
+      </c>
+      <c r="G38" t="s">
+        <v>207</v>
+      </c>
+      <c r="H38" t="s">
+        <v>211</v>
+      </c>
+      <c r="I38" t="s">
+        <v>208</v>
+      </c>
+      <c r="J38" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>215</v>
+      </c>
+      <c r="C39" t="s">
+        <v>216</v>
+      </c>
+      <c r="E39" t="s">
+        <v>51</v>
+      </c>
+      <c r="F39" t="s">
+        <v>209</v>
+      </c>
+      <c r="G39" t="s">
+        <v>208</v>
+      </c>
+      <c r="H39" t="s">
+        <v>214</v>
+      </c>
+      <c r="I39" t="s">
+        <v>217</v>
+      </c>
+      <c r="J39" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>218</v>
+      </c>
+      <c r="C40" t="s">
+        <v>219</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" t="s">
+        <v>220</v>
+      </c>
+      <c r="H40" t="s">
+        <v>105</v>
+      </c>
+      <c r="I40" t="s">
+        <v>221</v>
+      </c>
+      <c r="J40" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>223</v>
+      </c>
+      <c r="C41" t="s">
+        <v>224</v>
+      </c>
+      <c r="E41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" t="s">
+        <v>225</v>
+      </c>
+      <c r="G41" t="s">
+        <v>226</v>
+      </c>
+      <c r="H41" t="s">
+        <v>227</v>
+      </c>
+      <c r="I41" t="s">
+        <v>228</v>
+      </c>
+      <c r="J41" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>230</v>
+      </c>
+      <c r="C42" t="s">
+        <v>231</v>
+      </c>
+      <c r="E42" t="s">
+        <v>35</v>
+      </c>
+      <c r="F42" t="s">
+        <v>232</v>
+      </c>
+      <c r="G42" t="s">
+        <v>226</v>
+      </c>
+      <c r="H42" t="s">
+        <v>228</v>
+      </c>
+      <c r="I42" t="s">
+        <v>233</v>
+      </c>
+      <c r="J42" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>235</v>
+      </c>
+      <c r="C43" t="s">
+        <v>236</v>
+      </c>
+      <c r="E43" t="s">
+        <v>43</v>
+      </c>
+      <c r="F43" t="s">
+        <v>237</v>
+      </c>
+      <c r="G43" t="s">
+        <v>238</v>
+      </c>
+      <c r="H43" t="s">
+        <v>239</v>
+      </c>
+      <c r="I43" t="s">
+        <v>240</v>
+      </c>
+      <c r="J43" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" t="s">
+        <v>242</v>
+      </c>
+      <c r="E44" t="s">
+        <v>51</v>
+      </c>
+      <c r="F44" t="s">
+        <v>243</v>
+      </c>
+      <c r="G44" t="s">
+        <v>244</v>
+      </c>
+      <c r="H44" t="s">
+        <v>245</v>
+      </c>
+      <c r="I44" t="s">
+        <v>246</v>
+      </c>
+      <c r="J44" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>248</v>
+      </c>
+      <c r="C45" t="s">
+        <v>249</v>
+      </c>
+      <c r="E45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" t="s">
+        <v>250</v>
+      </c>
+      <c r="G45" t="s">
+        <v>251</v>
+      </c>
+      <c r="H45" t="s">
+        <v>252</v>
+      </c>
+      <c r="I45" t="s">
+        <v>253</v>
+      </c>
+      <c r="J45" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>255</v>
+      </c>
+      <c r="C46" t="s">
+        <v>256</v>
+      </c>
+      <c r="E46" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46" t="s">
+        <v>257</v>
+      </c>
+      <c r="G46" t="s">
+        <v>258</v>
+      </c>
+      <c r="H46" t="s">
+        <v>259</v>
+      </c>
+      <c r="I46" t="s">
+        <v>260</v>
+      </c>
+      <c r="J46" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C47" t="s">
+        <v>263</v>
+      </c>
+      <c r="E47" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" t="s">
+        <v>264</v>
+      </c>
+      <c r="G47" t="s">
+        <v>265</v>
+      </c>
+      <c r="H47" t="s">
+        <v>266</v>
+      </c>
+      <c r="I47" t="s">
+        <v>267</v>
+      </c>
+      <c r="J47" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>269</v>
+      </c>
+      <c r="C48" t="s">
+        <v>270</v>
+      </c>
+      <c r="E48" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48" t="s">
+        <v>266</v>
+      </c>
+      <c r="G48" t="s">
+        <v>265</v>
+      </c>
+      <c r="H48" t="s">
+        <v>267</v>
+      </c>
+      <c r="I48" t="s">
+        <v>264</v>
+      </c>
+      <c r="J48" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>272</v>
+      </c>
+      <c r="C49" t="s">
+        <v>273</v>
+      </c>
+      <c r="E49" t="s">
+        <v>51</v>
+      </c>
+      <c r="F49" t="s">
+        <v>274</v>
+      </c>
+      <c r="G49" t="s">
+        <v>275</v>
+      </c>
+      <c r="H49" t="s">
+        <v>276</v>
+      </c>
+      <c r="I49" t="s">
+        <v>277</v>
+      </c>
+      <c r="J49" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>279</v>
+      </c>
+      <c r="C50" t="s">
+        <v>280</v>
+      </c>
+      <c r="E50" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" t="s">
+        <v>281</v>
+      </c>
+      <c r="G50" t="s">
+        <v>282</v>
+      </c>
+      <c r="H50" t="s">
+        <v>283</v>
+      </c>
+      <c r="I50" t="s">
+        <v>284</v>
+      </c>
+      <c r="J50" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>286</v>
+      </c>
+      <c r="C51" t="s">
+        <v>287</v>
+      </c>
+      <c r="E51" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" t="s">
+        <v>288</v>
+      </c>
+      <c r="G51" t="s">
+        <v>289</v>
+      </c>
+      <c r="H51" t="s">
+        <v>290</v>
+      </c>
+      <c r="I51" t="s">
+        <v>291</v>
+      </c>
+      <c r="J51" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>293</v>
+      </c>
+      <c r="C52" t="s">
+        <v>294</v>
+      </c>
+      <c r="E52" t="s">
+        <v>35</v>
+      </c>
+      <c r="F52" t="s">
+        <v>295</v>
+      </c>
+      <c r="G52" t="s">
+        <v>296</v>
+      </c>
+      <c r="H52" t="s">
+        <v>297</v>
+      </c>
+      <c r="I52" t="s">
+        <v>298</v>
+      </c>
+      <c r="J52" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>300</v>
+      </c>
+      <c r="C53" t="s">
+        <v>301</v>
+      </c>
+      <c r="E53" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" t="s">
+        <v>302</v>
+      </c>
+      <c r="G53" t="s">
+        <v>303</v>
+      </c>
+      <c r="H53" t="s">
+        <v>304</v>
+      </c>
+      <c r="I53" t="s">
+        <v>305</v>
+      </c>
+      <c r="J53" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>307</v>
+      </c>
+      <c r="C54" t="s">
+        <v>308</v>
+      </c>
+      <c r="E54" t="s">
+        <v>51</v>
+      </c>
+      <c r="F54" t="s">
+        <v>297</v>
+      </c>
+      <c r="G54" t="s">
+        <v>309</v>
+      </c>
+      <c r="H54" t="s">
+        <v>310</v>
+      </c>
+      <c r="I54" t="s">
+        <v>311</v>
+      </c>
+      <c r="J54" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>312</v>
+      </c>
+      <c r="C55" t="s">
+        <v>313</v>
+      </c>
+      <c r="E55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" t="s">
+        <v>314</v>
+      </c>
+      <c r="G55" t="s">
+        <v>315</v>
+      </c>
+      <c r="H55" t="s">
+        <v>316</v>
+      </c>
+      <c r="I55" t="s">
+        <v>317</v>
+      </c>
+      <c r="J55" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>319</v>
+      </c>
+      <c r="C56" t="s">
+        <v>320</v>
+      </c>
+      <c r="E56" t="s">
+        <v>27</v>
+      </c>
+      <c r="F56" t="s">
+        <v>321</v>
+      </c>
+      <c r="G56" t="s">
+        <v>322</v>
+      </c>
+      <c r="H56" t="s">
+        <v>323</v>
+      </c>
+      <c r="I56" t="s">
+        <v>324</v>
+      </c>
+      <c r="J56" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>326</v>
+      </c>
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" t="s">
+        <v>327</v>
+      </c>
+      <c r="E57" t="s">
+        <v>35</v>
+      </c>
+      <c r="F57" t="s">
+        <v>328</v>
+      </c>
+      <c r="G57" t="s">
+        <v>329</v>
+      </c>
+      <c r="H57" t="s">
+        <v>330</v>
+      </c>
+      <c r="I57" t="s">
+        <v>331</v>
+      </c>
+      <c r="J57" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>333</v>
+      </c>
+      <c r="B58" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" t="s">
+        <v>334</v>
+      </c>
+      <c r="E58" t="s">
+        <v>43</v>
+      </c>
+      <c r="F58" t="s">
+        <v>335</v>
+      </c>
+      <c r="G58" t="s">
+        <v>336</v>
+      </c>
+      <c r="H58" t="s">
+        <v>337</v>
+      </c>
+      <c r="I58" t="s">
+        <v>338</v>
+      </c>
+      <c r="J58" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>340</v>
+      </c>
+      <c r="B59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" t="s">
+        <v>341</v>
+      </c>
+      <c r="E59" t="s">
+        <v>51</v>
+      </c>
+      <c r="F59" t="s">
+        <v>342</v>
+      </c>
+      <c r="G59" t="s">
+        <v>343</v>
+      </c>
+      <c r="H59" t="s">
+        <v>344</v>
+      </c>
+      <c r="I59" t="s">
+        <v>345</v>
+      </c>
+      <c r="J59" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>347</v>
+      </c>
+      <c r="B60" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" t="s">
+        <v>348</v>
+      </c>
+      <c r="E60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" t="s">
+        <v>349</v>
+      </c>
+      <c r="G60" t="s">
+        <v>350</v>
+      </c>
+      <c r="H60" t="s">
+        <v>351</v>
+      </c>
+      <c r="I60" t="s">
+        <v>352</v>
+      </c>
+      <c r="J60" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>353</v>
+      </c>
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" t="s">
+        <v>354</v>
+      </c>
+      <c r="E61" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61" t="s">
+        <v>335</v>
+      </c>
+      <c r="G61" t="s">
+        <v>355</v>
+      </c>
+      <c r="H61" t="s">
+        <v>356</v>
+      </c>
+      <c r="I61" t="s">
+        <v>336</v>
+      </c>
+      <c r="J61" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>358</v>
+      </c>
+      <c r="B62" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" t="s">
+        <v>359</v>
+      </c>
+      <c r="E62" t="s">
+        <v>35</v>
+      </c>
+      <c r="F62" t="s">
+        <v>338</v>
+      </c>
+      <c r="G62" t="s">
+        <v>356</v>
+      </c>
+      <c r="H62" t="s">
+        <v>336</v>
+      </c>
+      <c r="I62" t="s">
+        <v>357</v>
+      </c>
+      <c r="J62" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" t="s">
+        <v>361</v>
+      </c>
+      <c r="E63" t="s">
+        <v>43</v>
+      </c>
+      <c r="F63" t="s">
+        <v>335</v>
+      </c>
+      <c r="G63" t="s">
+        <v>338</v>
+      </c>
+      <c r="H63" t="s">
+        <v>356</v>
+      </c>
+      <c r="I63" t="s">
+        <v>337</v>
+      </c>
+      <c r="J63" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>362</v>
+      </c>
+      <c r="B64" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" t="s">
+        <v>363</v>
+      </c>
+      <c r="E64" t="s">
+        <v>51</v>
+      </c>
+      <c r="F64" t="s">
+        <v>297</v>
+      </c>
+      <c r="G64" t="s">
+        <v>364</v>
+      </c>
+      <c r="H64" t="s">
+        <v>295</v>
+      </c>
+      <c r="I64" t="s">
+        <v>357</v>
+      </c>
+      <c r="J64" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>365</v>
+      </c>
+      <c r="B65" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65" t="s">
+        <v>366</v>
+      </c>
+      <c r="E65" t="s">
+        <v>19</v>
+      </c>
+      <c r="F65" t="s">
+        <v>367</v>
+      </c>
+      <c r="G65" t="s">
+        <v>368</v>
+      </c>
+      <c r="H65" t="s">
+        <v>369</v>
+      </c>
+      <c r="I65" t="s">
+        <v>370</v>
+      </c>
+      <c r="J65" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>372</v>
+      </c>
+      <c r="B66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" t="s">
+        <v>373</v>
+      </c>
+      <c r="E66" t="s">
+        <v>27</v>
+      </c>
+      <c r="F66" t="s">
+        <v>374</v>
+      </c>
+      <c r="G66" t="s">
+        <v>375</v>
+      </c>
+      <c r="H66" t="s">
+        <v>376</v>
+      </c>
+      <c r="I66" t="s">
+        <v>377</v>
+      </c>
+      <c r="J66" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>379</v>
+      </c>
+      <c r="B67" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" t="s">
+        <v>380</v>
+      </c>
+      <c r="E67" t="s">
+        <v>35</v>
+      </c>
+      <c r="F67" t="s">
+        <v>381</v>
+      </c>
+      <c r="G67" t="s">
+        <v>382</v>
+      </c>
+      <c r="H67" t="s">
+        <v>383</v>
+      </c>
+      <c r="I67" t="s">
+        <v>310</v>
+      </c>
+      <c r="J67" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>384</v>
+      </c>
+      <c r="B68" t="s">
+        <v>17</v>
+      </c>
+      <c r="C68" t="s">
+        <v>385</v>
+      </c>
+      <c r="E68" t="s">
+        <v>43</v>
+      </c>
+      <c r="F68" t="s">
+        <v>356</v>
+      </c>
+      <c r="G68" t="s">
+        <v>335</v>
+      </c>
+      <c r="H68" t="s">
+        <v>386</v>
+      </c>
+      <c r="I68" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>387</v>
+      </c>
+      <c r="B69" t="s">
+        <v>17</v>
+      </c>
+      <c r="C69" t="s">
+        <v>388</v>
+      </c>
+      <c r="E69" t="s">
+        <v>51</v>
+      </c>
+      <c r="F69" t="s">
+        <v>389</v>
+      </c>
+      <c r="G69" t="s">
+        <v>390</v>
+      </c>
+      <c r="H69" t="s">
+        <v>391</v>
+      </c>
+      <c r="I69" t="s">
+        <v>392</v>
+      </c>
+      <c r="J69" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>394</v>
+      </c>
+      <c r="B70" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" t="s">
+        <v>395</v>
+      </c>
+      <c r="E70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" t="s">
+        <v>396</v>
+      </c>
+      <c r="G70" t="s">
+        <v>397</v>
+      </c>
+      <c r="H70" t="s">
+        <v>398</v>
+      </c>
+      <c r="I70" t="s">
+        <v>399</v>
+      </c>
+      <c r="J70" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A71" t="s">
+        <v>401</v>
+      </c>
+      <c r="B71" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71" t="s">
+        <v>402</v>
+      </c>
+      <c r="E71" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71" t="s">
+        <v>403</v>
+      </c>
+      <c r="G71" t="s">
+        <v>404</v>
+      </c>
+      <c r="H71" t="s">
+        <v>405</v>
+      </c>
+      <c r="I71" t="s">
+        <v>406</v>
+      </c>
+      <c r="J71" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A72" t="s">
+        <v>408</v>
+      </c>
+      <c r="B72" t="s">
+        <v>17</v>
+      </c>
+      <c r="C72" t="s">
+        <v>409</v>
+      </c>
+      <c r="E72" t="s">
+        <v>35</v>
+      </c>
+      <c r="F72" t="s">
+        <v>410</v>
+      </c>
+      <c r="G72" t="s">
+        <v>411</v>
+      </c>
+      <c r="H72" t="s">
+        <v>412</v>
+      </c>
+      <c r="I72" t="s">
+        <v>413</v>
+      </c>
+      <c r="J72" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
+        <v>415</v>
+      </c>
+      <c r="B73" t="s">
+        <v>17</v>
+      </c>
+      <c r="C73" t="s">
+        <v>416</v>
+      </c>
+      <c r="E73" t="s">
+        <v>43</v>
+      </c>
+      <c r="F73" t="s">
+        <v>417</v>
+      </c>
+      <c r="G73" t="s">
+        <v>418</v>
+      </c>
+      <c r="H73" t="s">
+        <v>419</v>
+      </c>
+      <c r="I73" t="s">
+        <v>356</v>
+      </c>
+      <c r="J73" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A74" t="s">
+        <v>421</v>
+      </c>
+      <c r="B74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74" t="s">
+        <v>422</v>
+      </c>
+      <c r="E74" t="s">
+        <v>51</v>
+      </c>
+      <c r="F74" t="s">
+        <v>423</v>
+      </c>
+      <c r="G74" t="s">
+        <v>424</v>
+      </c>
+      <c r="H74" t="s">
+        <v>425</v>
+      </c>
+      <c r="I74" t="s">
+        <v>426</v>
+      </c>
+      <c r="J74" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A75" t="s">
+        <v>428</v>
+      </c>
+      <c r="B75" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" t="s">
+        <v>429</v>
+      </c>
+      <c r="E75" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" t="s">
+        <v>430</v>
+      </c>
+      <c r="G75" t="s">
+        <v>316</v>
+      </c>
+      <c r="H75" t="s">
+        <v>431</v>
+      </c>
+      <c r="I75" t="s">
+        <v>432</v>
+      </c>
+      <c r="J75" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A76" t="s">
+        <v>433</v>
+      </c>
+      <c r="B76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" t="s">
+        <v>434</v>
+      </c>
+      <c r="E76" t="s">
+        <v>27</v>
+      </c>
+      <c r="F76" t="s">
+        <v>435</v>
+      </c>
+      <c r="G76" t="s">
+        <v>436</v>
+      </c>
+      <c r="H76" t="s">
+        <v>437</v>
+      </c>
+      <c r="I76" t="s">
+        <v>438</v>
+      </c>
+      <c r="J76" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A77" t="s">
+        <v>440</v>
+      </c>
+      <c r="B77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" t="s">
+        <v>441</v>
+      </c>
+      <c r="E77" t="s">
+        <v>35</v>
+      </c>
+      <c r="F77" t="s">
+        <v>302</v>
+      </c>
+      <c r="G77" t="s">
+        <v>305</v>
+      </c>
+      <c r="H77" t="s">
+        <v>442</v>
+      </c>
+      <c r="I77" t="s">
+        <v>303</v>
+      </c>
+      <c r="J77" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A78" t="s">
+        <v>443</v>
+      </c>
+      <c r="B78" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" t="s">
+        <v>444</v>
+      </c>
+      <c r="E78" t="s">
+        <v>43</v>
+      </c>
+      <c r="F78" t="s">
+        <v>445</v>
+      </c>
+      <c r="G78" t="s">
+        <v>446</v>
+      </c>
+      <c r="H78" t="s">
+        <v>447</v>
+      </c>
+      <c r="I78" t="s">
+        <v>448</v>
+      </c>
+      <c r="J78" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>450</v>
+      </c>
+      <c r="B79" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" t="s">
+        <v>451</v>
+      </c>
+      <c r="E79" t="s">
+        <v>51</v>
+      </c>
+      <c r="F79" t="s">
+        <v>452</v>
+      </c>
+      <c r="G79" t="s">
+        <v>453</v>
+      </c>
+      <c r="H79" t="s">
+        <v>454</v>
+      </c>
+      <c r="I79" t="s">
+        <v>455</v>
+      </c>
+      <c r="J79" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>457</v>
+      </c>
+      <c r="B80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" t="s">
+        <v>458</v>
+      </c>
+      <c r="E80" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" t="s">
+        <v>459</v>
+      </c>
+      <c r="G80" t="s">
+        <v>460</v>
+      </c>
+      <c r="H80" t="s">
+        <v>461</v>
+      </c>
+      <c r="I80" t="s">
+        <v>462</v>
+      </c>
+      <c r="J80" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>464</v>
+      </c>
+      <c r="B81" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" t="s">
+        <v>465</v>
+      </c>
+      <c r="E81" t="s">
+        <v>27</v>
+      </c>
+      <c r="F81" t="s">
+        <v>430</v>
+      </c>
+      <c r="G81" t="s">
+        <v>432</v>
+      </c>
+      <c r="H81" t="s">
+        <v>466</v>
+      </c>
+      <c r="I81" t="s">
+        <v>467</v>
+      </c>
+      <c r="J81" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>469</v>
+      </c>
+      <c r="B82" t="s">
+        <v>17</v>
+      </c>
+      <c r="C82" t="s">
+        <v>470</v>
+      </c>
+      <c r="E82" t="s">
+        <v>35</v>
+      </c>
+      <c r="F82" t="s">
+        <v>316</v>
+      </c>
+      <c r="G82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H82" t="s">
+        <v>471</v>
+      </c>
+      <c r="I82" t="s">
+        <v>432</v>
+      </c>
+      <c r="J82" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>473</v>
+      </c>
+      <c r="B83" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" t="s">
+        <v>474</v>
+      </c>
+      <c r="E83" t="s">
+        <v>43</v>
+      </c>
+      <c r="F83" t="s">
+        <v>475</v>
+      </c>
+      <c r="G83" t="s">
+        <v>476</v>
+      </c>
+      <c r="H83" t="s">
+        <v>477</v>
+      </c>
+      <c r="I83" t="s">
+        <v>478</v>
+      </c>
+      <c r="J83" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>480</v>
+      </c>
+      <c r="B84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" t="s">
+        <v>481</v>
+      </c>
+      <c r="E84" t="s">
+        <v>51</v>
+      </c>
+      <c r="F84" t="s">
+        <v>442</v>
+      </c>
+      <c r="G84" t="s">
+        <v>471</v>
+      </c>
+      <c r="H84" t="s">
+        <v>482</v>
+      </c>
+      <c r="I84" t="s">
+        <v>483</v>
+      </c>
+      <c r="J84" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>484</v>
+      </c>
+      <c r="B85" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" t="s">
+        <v>485</v>
+      </c>
+      <c r="E85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" t="s">
+        <v>486</v>
+      </c>
+      <c r="G85" t="s">
+        <v>487</v>
+      </c>
+      <c r="H85" t="s">
+        <v>488</v>
+      </c>
+      <c r="I85" t="s">
+        <v>489</v>
+      </c>
+      <c r="J85" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>491</v>
+      </c>
+      <c r="B86" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86" t="s">
+        <v>492</v>
+      </c>
+      <c r="E86" t="s">
+        <v>27</v>
+      </c>
+      <c r="F86" t="s">
+        <v>493</v>
+      </c>
+      <c r="G86" t="s">
+        <v>494</v>
+      </c>
+      <c r="H86" t="s">
+        <v>495</v>
+      </c>
+      <c r="I86" t="s">
+        <v>496</v>
+      </c>
+      <c r="J86" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A87" t="s">
+        <v>498</v>
+      </c>
+      <c r="B87" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" t="s">
+        <v>499</v>
+      </c>
+      <c r="E87" t="s">
+        <v>35</v>
+      </c>
+      <c r="F87" t="s">
+        <v>500</v>
+      </c>
+      <c r="G87" t="s">
+        <v>501</v>
+      </c>
+      <c r="H87" t="s">
+        <v>502</v>
+      </c>
+      <c r="I87" t="s">
+        <v>503</v>
+      </c>
+      <c r="J87" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A88" t="s">
+        <v>505</v>
+      </c>
+      <c r="B88" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" t="s">
+        <v>506</v>
+      </c>
+      <c r="E88" t="s">
+        <v>43</v>
+      </c>
+      <c r="F88" t="s">
+        <v>507</v>
+      </c>
+      <c r="G88" t="s">
+        <v>508</v>
+      </c>
+      <c r="H88" t="s">
+        <v>509</v>
+      </c>
+      <c r="I88" t="s">
+        <v>510</v>
+      </c>
+      <c r="J88" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>512</v>
+      </c>
+      <c r="B89" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" t="s">
+        <v>513</v>
+      </c>
+      <c r="E89" t="s">
+        <v>51</v>
+      </c>
+      <c r="F89" t="s">
+        <v>514</v>
+      </c>
+      <c r="G89" t="s">
+        <v>515</v>
+      </c>
+      <c r="H89" t="s">
+        <v>516</v>
+      </c>
+      <c r="I89" t="s">
+        <v>517</v>
+      </c>
+      <c r="J89" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>519</v>
+      </c>
+      <c r="B90" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" t="s">
+        <v>520</v>
+      </c>
+      <c r="E90" t="s">
+        <v>19</v>
+      </c>
+      <c r="F90" t="s">
+        <v>521</v>
+      </c>
+      <c r="G90" t="s">
+        <v>522</v>
+      </c>
+      <c r="H90" t="s">
+        <v>523</v>
+      </c>
+      <c r="I90" t="s">
+        <v>446</v>
+      </c>
+      <c r="J90" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>525</v>
+      </c>
+      <c r="B91" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" t="s">
+        <v>526</v>
+      </c>
+      <c r="E91" t="s">
+        <v>27</v>
+      </c>
+      <c r="F91" t="s">
+        <v>527</v>
+      </c>
+      <c r="G91" t="s">
+        <v>528</v>
+      </c>
+      <c r="H91" t="s">
+        <v>529</v>
+      </c>
+      <c r="I91" t="s">
+        <v>530</v>
+      </c>
+      <c r="J91" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A92" t="s">
+        <v>532</v>
+      </c>
+      <c r="B92" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" t="s">
+        <v>533</v>
+      </c>
+      <c r="E92" t="s">
+        <v>35</v>
+      </c>
+      <c r="F92" t="s">
+        <v>315</v>
+      </c>
+      <c r="G92" t="s">
+        <v>316</v>
+      </c>
+      <c r="H92" t="s">
+        <v>534</v>
+      </c>
+      <c r="I92" t="s">
+        <v>317</v>
+      </c>
+      <c r="J92" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>536</v>
+      </c>
+      <c r="B93" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" t="s">
+        <v>537</v>
+      </c>
+      <c r="E93" t="s">
+        <v>43</v>
+      </c>
+      <c r="F93" t="s">
+        <v>538</v>
+      </c>
+      <c r="G93" t="s">
+        <v>517</v>
+      </c>
+      <c r="H93" t="s">
+        <v>539</v>
+      </c>
+      <c r="I93" t="s">
+        <v>540</v>
+      </c>
+      <c r="J93" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>542</v>
+      </c>
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" t="s">
+        <v>543</v>
+      </c>
+      <c r="E94" t="s">
+        <v>43</v>
+      </c>
+      <c r="F94" t="s">
+        <v>544</v>
+      </c>
+      <c r="G94" t="s">
+        <v>545</v>
+      </c>
+      <c r="H94" t="s">
+        <v>546</v>
+      </c>
+      <c r="I94" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>548</v>
+      </c>
+      <c r="B95" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" t="s">
+        <v>549</v>
+      </c>
+      <c r="E95" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" t="s">
+        <v>550</v>
+      </c>
+      <c r="G95" t="s">
+        <v>551</v>
+      </c>
+      <c r="H95" t="s">
+        <v>552</v>
+      </c>
+      <c r="I95" t="s">
+        <v>553</v>
+      </c>
+      <c r="J95" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>555</v>
+      </c>
+      <c r="B96" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" t="s">
+        <v>556</v>
+      </c>
+      <c r="E96" t="s">
+        <v>27</v>
+      </c>
+      <c r="F96" t="s">
+        <v>557</v>
+      </c>
+      <c r="G96" t="s">
+        <v>558</v>
+      </c>
+      <c r="H96" t="s">
+        <v>559</v>
+      </c>
+      <c r="I96" t="s">
+        <v>560</v>
+      </c>
+      <c r="J96" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>562</v>
+      </c>
+      <c r="B97" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" t="s">
+        <v>563</v>
+      </c>
+      <c r="E97" t="s">
+        <v>35</v>
+      </c>
+      <c r="F97" t="s">
+        <v>564</v>
+      </c>
+      <c r="G97" t="s">
+        <v>565</v>
+      </c>
+      <c r="H97" t="s">
+        <v>566</v>
+      </c>
+      <c r="I97" t="s">
+        <v>567</v>
+      </c>
+      <c r="J97" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>569</v>
+      </c>
+      <c r="B98" t="s">
+        <v>17</v>
+      </c>
+      <c r="C98" t="s">
+        <v>570</v>
+      </c>
+      <c r="E98" t="s">
+        <v>43</v>
+      </c>
+      <c r="F98" t="s">
+        <v>571</v>
+      </c>
+      <c r="G98" t="s">
+        <v>572</v>
+      </c>
+      <c r="H98" t="s">
+        <v>573</v>
+      </c>
+      <c r="I98" t="s">
+        <v>574</v>
+      </c>
+      <c r="J98" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>576</v>
+      </c>
+      <c r="B99" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" t="s">
+        <v>577</v>
+      </c>
+      <c r="E99" t="s">
+        <v>51</v>
+      </c>
+      <c r="F99" t="s">
+        <v>578</v>
+      </c>
+      <c r="G99" t="s">
+        <v>579</v>
+      </c>
+      <c r="H99" t="s">
+        <v>580</v>
+      </c>
+      <c r="I99" t="s">
+        <v>581</v>
+      </c>
+      <c r="J99" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>583</v>
+      </c>
+      <c r="B100" t="s">
+        <v>17</v>
+      </c>
+      <c r="C100" t="s">
+        <v>584</v>
+      </c>
+      <c r="E100" t="s">
+        <v>19</v>
+      </c>
+      <c r="F100" t="s">
+        <v>585</v>
+      </c>
+      <c r="G100" t="s">
+        <v>586</v>
+      </c>
+      <c r="H100" t="s">
+        <v>587</v>
+      </c>
+      <c r="I100" t="s">
+        <v>588</v>
+      </c>
+      <c r="J100" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>590</v>
+      </c>
+      <c r="B101" t="s">
+        <v>17</v>
+      </c>
+      <c r="C101" t="s">
+        <v>591</v>
+      </c>
+      <c r="E101" t="s">
+        <v>27</v>
+      </c>
+      <c r="F101" t="s">
+        <v>592</v>
+      </c>
+      <c r="G101" t="s">
+        <v>593</v>
+      </c>
+      <c r="H101" t="s">
+        <v>594</v>
+      </c>
+      <c r="I101" t="s">
+        <v>595</v>
+      </c>
+      <c r="J101" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>597</v>
+      </c>
+      <c r="B102" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" t="s">
+        <v>598</v>
+      </c>
+      <c r="E102" t="s">
+        <v>35</v>
+      </c>
+      <c r="F102" t="s">
+        <v>599</v>
+      </c>
+      <c r="G102" t="s">
+        <v>600</v>
+      </c>
+      <c r="H102" t="s">
+        <v>601</v>
+      </c>
+      <c r="I102" t="s">
+        <v>602</v>
+      </c>
+      <c r="J102" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>604</v>
+      </c>
+      <c r="B103" t="s">
+        <v>17</v>
+      </c>
+      <c r="C103" t="s">
+        <v>605</v>
+      </c>
+      <c r="E103" t="s">
+        <v>43</v>
+      </c>
+      <c r="F103" t="s">
+        <v>606</v>
+      </c>
+      <c r="G103" t="s">
+        <v>594</v>
+      </c>
+      <c r="H103" t="s">
+        <v>595</v>
+      </c>
+      <c r="I103" t="s">
+        <v>607</v>
+      </c>
+      <c r="J103" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>609</v>
+      </c>
+      <c r="B104" t="s">
+        <v>17</v>
+      </c>
+      <c r="C104" t="s">
+        <v>610</v>
+      </c>
+      <c r="E104" t="s">
+        <v>51</v>
+      </c>
+      <c r="F104" t="s">
+        <v>611</v>
+      </c>
+      <c r="G104" t="s">
+        <v>612</v>
+      </c>
+      <c r="H104" t="s">
+        <v>613</v>
+      </c>
+      <c r="I104" t="s">
+        <v>614</v>
+      </c>
+      <c r="J104" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>616</v>
+      </c>
+      <c r="B105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C105" t="s">
+        <v>617</v>
+      </c>
+      <c r="E105" t="s">
+        <v>19</v>
+      </c>
+      <c r="F105" t="s">
+        <v>618</v>
+      </c>
+      <c r="G105" t="s">
+        <v>619</v>
+      </c>
+      <c r="H105" t="s">
+        <v>620</v>
+      </c>
+      <c r="I105" t="s">
+        <v>621</v>
+      </c>
+      <c r="J105" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>623</v>
+      </c>
+      <c r="B106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" t="s">
+        <v>624</v>
+      </c>
+      <c r="E106" t="s">
+        <v>27</v>
+      </c>
+      <c r="F106" t="s">
+        <v>625</v>
+      </c>
+      <c r="G106" t="s">
+        <v>595</v>
+      </c>
+      <c r="H106" t="s">
+        <v>626</v>
+      </c>
+      <c r="I106" t="s">
+        <v>627</v>
+      </c>
+      <c r="J106" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>629</v>
+      </c>
+      <c r="B107" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107" t="s">
+        <v>630</v>
+      </c>
+      <c r="E107" t="s">
+        <v>35</v>
+      </c>
+      <c r="F107" t="s">
+        <v>631</v>
+      </c>
+      <c r="G107" t="s">
+        <v>632</v>
+      </c>
+      <c r="H107" t="s">
+        <v>633</v>
+      </c>
+      <c r="I107" t="s">
+        <v>634</v>
+      </c>
+      <c r="J107" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>636</v>
+      </c>
+      <c r="B108" t="s">
+        <v>17</v>
+      </c>
+      <c r="C108" t="s">
+        <v>637</v>
+      </c>
+      <c r="E108" t="s">
+        <v>43</v>
+      </c>
+      <c r="F108" t="s">
+        <v>606</v>
+      </c>
+      <c r="G108" t="s">
+        <v>638</v>
+      </c>
+      <c r="H108" t="s">
+        <v>594</v>
+      </c>
+      <c r="I108" t="s">
+        <v>595</v>
+      </c>
+      <c r="J108" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>639</v>
+      </c>
+      <c r="B109" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" t="s">
+        <v>640</v>
+      </c>
+      <c r="E109" t="s">
+        <v>51</v>
+      </c>
+      <c r="F109" t="s">
+        <v>641</v>
+      </c>
+      <c r="G109" t="s">
+        <v>642</v>
+      </c>
+      <c r="H109" t="s">
+        <v>643</v>
+      </c>
+      <c r="I109" t="s">
+        <v>644</v>
+      </c>
+      <c r="J109" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>646</v>
+      </c>
+      <c r="B110" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" t="s">
+        <v>647</v>
+      </c>
+      <c r="E110" t="s">
+        <v>19</v>
+      </c>
+      <c r="F110" t="s">
+        <v>648</v>
+      </c>
+      <c r="G110" t="s">
+        <v>649</v>
+      </c>
+      <c r="H110" t="s">
+        <v>650</v>
+      </c>
+      <c r="I110" t="s">
+        <v>651</v>
+      </c>
+      <c r="J110" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>653</v>
+      </c>
+      <c r="B111" t="s">
+        <v>17</v>
+      </c>
+      <c r="C111" t="s">
+        <v>654</v>
+      </c>
+      <c r="E111" t="s">
+        <v>27</v>
+      </c>
+      <c r="F111" t="s">
+        <v>655</v>
+      </c>
+      <c r="G111" t="s">
+        <v>656</v>
+      </c>
+      <c r="H111" t="s">
+        <v>657</v>
+      </c>
+      <c r="I111" t="s">
+        <v>658</v>
+      </c>
+      <c r="J111" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>660</v>
+      </c>
+      <c r="B112" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" t="s">
+        <v>661</v>
+      </c>
+      <c r="E112" t="s">
+        <v>35</v>
+      </c>
+      <c r="F112" t="s">
+        <v>662</v>
+      </c>
+      <c r="G112" t="s">
+        <v>663</v>
+      </c>
+      <c r="H112" t="s">
+        <v>664</v>
+      </c>
+      <c r="I112" t="s">
+        <v>665</v>
+      </c>
+      <c r="J112" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>667</v>
+      </c>
+      <c r="B113" t="s">
+        <v>17</v>
+      </c>
+      <c r="C113" t="s">
+        <v>668</v>
+      </c>
+      <c r="D113" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" t="s">
+        <v>43</v>
+      </c>
+      <c r="F113" t="s">
+        <v>390</v>
+      </c>
+      <c r="G113" t="s">
+        <v>669</v>
+      </c>
+      <c r="H113" t="s">
+        <v>670</v>
+      </c>
+      <c r="I113" t="s">
+        <v>671</v>
+      </c>
+      <c r="J113" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
+        <v>672</v>
+      </c>
+      <c r="B114" t="s">
+        <v>17</v>
+      </c>
+      <c r="C114" t="s">
+        <v>673</v>
+      </c>
+      <c r="D114" t="s">
+        <v>17</v>
+      </c>
+      <c r="E114" t="s">
+        <v>51</v>
+      </c>
+      <c r="F114" t="s">
+        <v>674</v>
+      </c>
+      <c r="G114" t="s">
+        <v>675</v>
+      </c>
+      <c r="H114" t="s">
+        <v>676</v>
+      </c>
+      <c r="I114" t="s">
+        <v>677</v>
+      </c>
+      <c r="J114" t="s">
+        <v>678</v>
       </c>
     </row>
   </sheetData>

--- a/publish/Radhika_Nepali/questions.xlsx
+++ b/publish/Radhika_Nepali/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anuj\opnsrc_try\ai\QuizWeb_Manual\publish\Radhika_Nepali\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0B4FB9-0E7D-4896-834E-B15F5B7766FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1AD524-592F-4366-BB93-71C7C3A8A700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Class: 9</t>
   </si>
@@ -70,79 +70,100 @@
     <t>Option8</t>
   </si>
   <si>
-    <t/>
+    <t>1</t>
+  </si>
+  <si>
+    <t>What does HTML stand for?</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>HyperText Markup Language</t>
+  </si>
+  <si>
+    <t>High Tech Modern Language</t>
+  </si>
+  <si>
+    <t>Hyperlink and Text Management Language</t>
+  </si>
+  <si>
+    <t>Home Tool Markup Language</t>
+  </si>
+  <si>
+    <t>Hyper Transfer Markup Language</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>HTML is a markup language used to create:</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Operating systems</t>
+  </si>
+  <si>
+    <t>Web pages and websites</t>
+  </si>
+  <si>
+    <t>Desktop applications only</t>
+  </si>
+  <si>
+    <t>Databases</t>
+  </si>
+  <si>
+    <t>Network cables</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Which tag is used to create a hyperlink in HTML?</t>
   </si>
   <si>
     <t>C</t>
   </si>
   <si>
+    <t>&lt;link&gt;</t>
+  </si>
+  <si>
+    <t>&lt;href&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;url&gt;</t>
+  </si>
+  <si>
+    <t>&lt;hyper&gt;</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Which attribute specifies the destination address of a link in HTML?</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>css</t>
-  </si>
-  <si>
-    <t>www</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>HTML files are usually saved with the file extension:</t>
-  </si>
-  <si>
-    <t>.pdf</t>
-  </si>
-  <si>
-    <t>.jpg</t>
-  </si>
-  <si>
-    <t>.html</t>
-  </si>
-  <si>
-    <t>.docx</t>
-  </si>
-  <si>
-    <t>.exe</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>Which of the following is a top-level domain?</t>
-  </si>
-  <si>
-    <t>http</t>
-  </si>
-  <si>
-    <t>html</t>
-  </si>
-  <si>
-    <t>.com</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>An ordered list in HTML displays items with:</t>
-  </si>
-  <si>
-    <t>Circles</t>
-  </si>
-  <si>
-    <t>Squares</t>
-  </si>
-  <si>
-    <t>Dashes</t>
-  </si>
-  <si>
-    <t>Check marks</t>
-  </si>
-  <si>
-    <t>Numbers</t>
+    <t>src</t>
+  </si>
+  <si>
+    <t>alt</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>href</t>
+  </si>
+  <si>
+    <t>hl</t>
   </si>
 </sst>
 </file>
@@ -983,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
@@ -1044,95 +1065,106 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="J5" t="s">
         <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="I6" t="s">
         <v>30</v>
       </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="J6" t="s">
         <v>31</v>
-      </c>
-      <c r="H6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
         <v>35</v>
       </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>36</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>37</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>38</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>39</v>
       </c>
-      <c r="J7" t="s">
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
         <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
